--- a/templates/sanitaire_2wc_pmr.xlsx
+++ b/templates/sanitaire_2wc_pmr.xlsx
@@ -1,61 +1,278 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\assist.compta\AppData\Local\Temp\claude\P--Joris\87be7f81-e737-4d81-918c-2f40dacc0bcb\scratchpad\modeles_reels_new\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{70C85CA8-EDF6-42CB-8E6C-23EC4383FFC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6687E1F3-2D98-4053-8D1F-1E3BD75D0E49}"/>
   </bookViews>
   <sheets>
-    <sheet name="Etat des lieux" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2WCH" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="125725"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="50">
+  <si>
+    <t>ETAT INTERIEUR</t>
+  </si>
+  <si>
+    <t>Porte</t>
+  </si>
+  <si>
+    <t>Radiateur</t>
+  </si>
+  <si>
+    <t>Urinoir</t>
+  </si>
+  <si>
+    <t>Miroir</t>
+  </si>
+  <si>
+    <t>ETAT EXTERIEUR</t>
+  </si>
+  <si>
+    <t>Longpan AR</t>
+  </si>
+  <si>
+    <t>Longpan AV</t>
+  </si>
+  <si>
+    <t>Légende</t>
+  </si>
+  <si>
+    <t>Enfoncement :      x</t>
+  </si>
+  <si>
+    <t>Rayure :      /</t>
+  </si>
+  <si>
+    <t>Trou :      o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W ….…………..…..   S ………….……. </t>
+  </si>
+  <si>
+    <t>Panneaux</t>
+  </si>
+  <si>
+    <t>Début de loc</t>
+  </si>
+  <si>
+    <t>Fin de loc</t>
+  </si>
+  <si>
+    <t>………………………………………………</t>
+  </si>
+  <si>
+    <t>Portes</t>
+  </si>
+  <si>
+    <t>Date, Nom et Signature</t>
+  </si>
+  <si>
+    <t>Signature précédée mention "bon pour accord"</t>
+  </si>
+  <si>
+    <t>Luminaire</t>
+  </si>
+  <si>
+    <t>Interrupteur</t>
+  </si>
+  <si>
+    <t>Chauffe-eau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coffret électrique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">          Pignon D</t>
+  </si>
+  <si>
+    <t>Pignon G</t>
+  </si>
+  <si>
+    <t>……………..</t>
+  </si>
+  <si>
+    <t>CLEF :  OUI        NON</t>
+  </si>
+  <si>
+    <t>Sol</t>
+  </si>
+  <si>
+    <t>Lavabo + robinets</t>
+  </si>
+  <si>
+    <t>Groupe de sécurité</t>
+  </si>
+  <si>
+    <t>Fenêtre</t>
+  </si>
+  <si>
+    <t>Cuvette</t>
+  </si>
+  <si>
+    <t>Abattant cuvette</t>
+  </si>
+  <si>
+    <t>Chasse d’eau</t>
+  </si>
+  <si>
+    <t>Dévidoir papier</t>
+  </si>
+  <si>
+    <t>Rampe handi</t>
+  </si>
+  <si>
+    <t>ETAT DES LIEUX</t>
+  </si>
+  <si>
+    <t>MATERIEL A ASSURER PAR VOS SOINS (VOL, INCENDIE, BRIS DE GLACE, DEGATS DES EAUX.)</t>
+  </si>
+  <si>
+    <t>PVC observations</t>
+  </si>
+  <si>
+    <t>Arrivée</t>
+  </si>
+  <si>
+    <t>Evacuation</t>
+  </si>
+  <si>
+    <t>CHENEAUX NETTOYES   OUI    NON</t>
+  </si>
+  <si>
+    <t>CLIENT :</t>
+  </si>
+  <si>
+    <t>1WC</t>
+  </si>
+  <si>
+    <t>1WC Handi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHANTIER : </t>
+  </si>
+  <si>
+    <t>Sanitaire : 2WC dont 1 PMR + 2 LAVABOS</t>
+  </si>
+  <si>
+    <t>Nom préparateur :                                         Visa contrôleur :                                          Date :</t>
+  </si>
+  <si>
+    <t>OUI</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="13"/>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
+      <sz val="12"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00888888"/>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="11"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFEFEF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
+        <fgColor indexed="22"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -64,109 +281,1110 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="00BBBBBB"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BBBBBB"/>
+        <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="104">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1121" name="Text Box 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2393788-2605-C4F2-58D5-6B123A88A9EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3190875" y="161925"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>PIGNON </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1123" name="Text Box 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F5131BE-D1B9-BDA4-05CC-5B619753E679}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="304800" y="161925"/>
+          <a:ext cx="657225" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>Longpan AV</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1163" name="Text Box 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B49B8E8E-0034-BC45-4F11-B15FBF0C05B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6934200" y="161925"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="fr-FR" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:rPr>
+            <a:t>Longpan AR</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>742950</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1164" name="Rectangle 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA04F5F3-7B19-2197-5F97-9509A0DFF36C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4210050" y="2428875"/>
+          <a:ext cx="1552575" cy="1085850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>704850</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>895350</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1165" name="Rectangle 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F229A312-7A7D-663D-E763-04873E9E4BD1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="704850" y="2466975"/>
+          <a:ext cx="1552575" cy="1047750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:scene3d>
+          <a:camera prst="legacyPerspectiveFront">
+            <a:rot lat="600000" lon="2100000" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="legacyFlat2" dir="b"/>
+        </a:scene3d>
+        <a:sp3d extrusionH="1801800" prstMaterial="legacyMatte">
+          <a:bevelT w="13500" h="13500" prst="angle"/>
+          <a:bevelB w="13500" h="13500" prst="angle"/>
+          <a:extrusionClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:extrusionClr>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1166" name="Image 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8214FF54-CA70-737A-D06A-C417EA980A6C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="24324"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19050" y="47625"/>
+          <a:ext cx="2733675" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -443,83 +1661,800 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1" cy="1"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </a:spPr>
+      <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="0" rIns="0" bIns="0" upright="1"/>
+      <a:lstStyle/>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1" cy="1"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </a:spPr>
+      <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="0" rIns="0" bIns="0" upright="1"/>
+      <a:lstStyle/>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FF010A4-5691-4869-89AA-F8115BAA0917}">
+  <sheetPr codeName="Feuil4">
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A2:H61"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="11.42578125" style="9"/>
+    <col min="2" max="2" width="9" style="9" customWidth="1"/>
+    <col min="3" max="7" width="13.7109375" style="9" customWidth="1"/>
+    <col min="8" max="8" width="15" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ÉTAT DES LIEUX — sanitaire_2wc_pmr.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Client</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Chantier</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Adresse</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Code postal</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Ville</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>État réel / Réserves / Signatures — NON pré-rempli (rempli à la main)</t>
-        </is>
-      </c>
+    <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E2" s="96" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+    </row>
+    <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+    </row>
+    <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E5" s="97" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="103" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="100"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="100"/>
+      <c r="H6" s="100"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="19"/>
+      <c r="B7" s="18"/>
+      <c r="E7" s="97" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="97"/>
+      <c r="G7" s="97"/>
+      <c r="H7" s="97"/>
+    </row>
+    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="98" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="98"/>
+    </row>
+    <row r="9" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="E9" s="17"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="17"/>
+    </row>
+    <row r="10" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="101" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="102"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="74"/>
+    </row>
+    <row r="11" spans="1:8" ht="2.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D12" s="43"/>
+      <c r="F12" s="99" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="86"/>
+      <c r="B19" s="86"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="87" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="88"/>
+      <c r="C24" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="89"/>
+      <c r="E24" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="32"/>
+      <c r="G24" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="23"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="47"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="73"/>
+      <c r="E25" s="74"/>
+      <c r="F25" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="73"/>
+      <c r="H25" s="74"/>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="33"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="62"/>
+      <c r="E26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="62"/>
+      <c r="H26" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="91"/>
+      <c r="C27" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="58"/>
+      <c r="E27" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="58"/>
+      <c r="H27" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="92"/>
+      <c r="B28" s="93"/>
+      <c r="C28" s="59"/>
+      <c r="D28" s="60"/>
+      <c r="E28" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="F28" s="59"/>
+      <c r="G28" s="60"/>
+      <c r="H28" s="28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="58"/>
+      <c r="C29" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="58"/>
+      <c r="E29" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="58"/>
+      <c r="H29" s="29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="59"/>
+      <c r="B30" s="60"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="F30" s="59"/>
+      <c r="G30" s="60"/>
+      <c r="H30" s="29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="94" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="95"/>
+      <c r="C31" s="84" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="90"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="84" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" s="90"/>
+      <c r="H31" s="85"/>
+    </row>
+    <row r="32" spans="1:8" s="1" customFormat="1" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="20"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="32"/>
+    </row>
+    <row r="33" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="68"/>
+      <c r="C33" s="68"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="68"/>
+      <c r="F33" s="68"/>
+      <c r="G33" s="68"/>
+      <c r="H33" s="31"/>
+    </row>
+    <row r="34" spans="1:8" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="73"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="73"/>
+      <c r="H34" s="74"/>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="62"/>
+      <c r="E35" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F35" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="62"/>
+      <c r="H35" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" s="70"/>
+      <c r="C36" s="63"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+    </row>
+    <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="65"/>
+      <c r="B37" s="71"/>
+      <c r="C37" s="65"/>
+      <c r="D37" s="66"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+    </row>
+    <row r="38" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="82" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" s="83"/>
+      <c r="C38" s="84"/>
+      <c r="D38" s="85"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+    </row>
+    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="69" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" s="77"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+    </row>
+    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="75" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40" s="76"/>
+      <c r="C40" s="51"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+    </row>
+    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="75" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" s="76"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+    </row>
+    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="75" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" s="76"/>
+      <c r="C42" s="51"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+    </row>
+    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="B43" s="76"/>
+      <c r="C43" s="51"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+    </row>
+    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="75" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" s="76"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+    </row>
+    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="75" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" s="76"/>
+      <c r="C45" s="51"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+    </row>
+    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="75" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46" s="76"/>
+      <c r="C46" s="51"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+    </row>
+    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="B47" s="76"/>
+      <c r="C47" s="51"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+    </row>
+    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="B48" s="76"/>
+      <c r="C48" s="51"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+    </row>
+    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="76"/>
+      <c r="C49" s="51"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+    </row>
+    <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="76"/>
+      <c r="C50" s="51"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+    </row>
+    <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" s="76"/>
+      <c r="C51" s="51"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+    </row>
+    <row r="52" spans="1:8" s="7" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" s="76"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="42"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="42"/>
+      <c r="H52" s="42"/>
+    </row>
+    <row r="53" spans="1:8" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="78"/>
+      <c r="C53" s="39"/>
+      <c r="D53" s="40"/>
+      <c r="E53" s="40"/>
+      <c r="F53" s="39"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="41"/>
+    </row>
+    <row r="54" spans="1:8" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="B54" s="78"/>
+      <c r="C54" s="36"/>
+      <c r="D54" s="37"/>
+      <c r="E54" s="37"/>
+      <c r="F54" s="36"/>
+      <c r="G54" s="37"/>
+      <c r="H54" s="38"/>
+    </row>
+    <row r="55" spans="1:8" s="7" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="76"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="33"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="35"/>
+    </row>
+    <row r="56" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="69" t="s">
+        <v>36</v>
+      </c>
+      <c r="B56" s="77"/>
+      <c r="C56" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="22"/>
+    </row>
+    <row r="57" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="80" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="81"/>
+      <c r="C57" s="81"/>
+      <c r="D57" s="81"/>
+      <c r="E57" s="81"/>
+      <c r="F57" s="81"/>
+      <c r="G57" s="81"/>
+      <c r="H57" s="74"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" s="76" t="s">
+        <v>18</v>
+      </c>
+      <c r="B58" s="76"/>
+      <c r="C58" s="76"/>
+      <c r="D58" s="76"/>
+      <c r="E58" s="76" t="s">
+        <v>18</v>
+      </c>
+      <c r="F58" s="76"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="76"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="B60" s="79"/>
+      <c r="C60" s="79"/>
+      <c r="D60" s="79"/>
+      <c r="E60" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" s="79"/>
+      <c r="G60" s="79"/>
+      <c r="H60" s="79"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" s="10"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="70">
+    <mergeCell ref="E2:H4"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D28"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="F27:G28"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="F29:G30"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="C36:D37"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A36:B37"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C41:D41"/>
+  </mergeCells>
+  <phoneticPr fontId="0" type="noConversion"/>
+  <pageMargins left="0.27559055118110237" right="0.23622047244094488" top="0.27559055118110237" bottom="0.11811023622047244" header="0.27559055118110237" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="97" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>